--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1457,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113687809</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56808</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartsjökullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>659451</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7079668</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>113687809</v>
       </c>
       <c r="B9" t="n">
-        <v>56808</v>
+        <v>56810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1578,11 +1578,11 @@
         <v>119368781</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1578,7 +1578,7 @@
         <v>119368781</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1578,7 +1578,7 @@
         <v>119368781</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1578,7 +1578,7 @@
         <v>119368781</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1578,7 +1578,7 @@
         <v>119368781</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1462,12 +1462,7 @@
         <v>113687809</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,6 +1488,10 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svartsjökullen, Ång</t>
@@ -1564,12 +1563,12 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>113687809</v>
       </c>
       <c r="B9" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>113687809</v>
       </c>
       <c r="B9" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 69250-2021 artfynd.xlsx
+++ b/artfynd/A 69250-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96989079</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988088</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988730</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988733</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988768</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988589</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96988341</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113687809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,8 +1839,26 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119368781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>